--- a/assets/LLM_Smart_Contract_Venues_Perfect.xlsx
+++ b/assets/LLM_Smart_Contract_Venues_Perfect.xlsx
@@ -578,12 +578,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -619,6 +619,11 @@
           <t>官网/主页链接</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>openalex_source_id</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -800,7 +805,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>CCF T2 (高认可)</t>
+          <t>--</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>CCF 交叉/C</t>
+          <t>--</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1222,7 +1227,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Internet of Things - *位置修正*</t>
+          <t>Internet of Things</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -1238,6 +1243,11 @@
       <c r="E24" s="17" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/journal/internet-of-things</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S4210174276</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1296,7 @@
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>CCF C</t>
+          <t>--</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -1303,7 +1313,7 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>Computers</t>
+          <t>Computers (MDPI)</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
@@ -1319,6 +1329,11 @@
       <c r="E27" s="20" t="inlineStr">
         <is>
           <t>https://www.mdpi.com/journal/computers</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S4210228075</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1345,7 @@
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Information (MDPI)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -1346,6 +1361,11 @@
       <c r="E28" s="23" t="inlineStr">
         <is>
           <t>https://www.mdpi.com/journal/information</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S4210219776</t>
         </is>
       </c>
     </row>
@@ -1378,46 +1398,46 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink ref="E2" ns1:id="rId1"/>
+    <hyperlink ref="E3" ns1:id="rId2"/>
+    <hyperlink ref="E4" ns1:id="rId3"/>
+    <hyperlink ref="E5" ns1:id="rId4"/>
+    <hyperlink ref="E6" ns1:id="rId5"/>
+    <hyperlink ref="E7" ns1:id="rId6"/>
+    <hyperlink ref="E8" ns1:id="rId7"/>
+    <hyperlink ref="E9" ns1:id="rId8"/>
+    <hyperlink ref="E10" ns1:id="rId9"/>
+    <hyperlink ref="E11" ns1:id="rId10"/>
+    <hyperlink ref="E12" ns1:id="rId11"/>
+    <hyperlink ref="E13" ns1:id="rId12"/>
+    <hyperlink ref="E14" ns1:id="rId13"/>
+    <hyperlink ref="E15" ns1:id="rId14"/>
+    <hyperlink ref="E16" ns1:id="rId15"/>
+    <hyperlink ref="E17" ns1:id="rId16"/>
+    <hyperlink ref="E18" ns1:id="rId17"/>
+    <hyperlink ref="E19" ns1:id="rId18"/>
+    <hyperlink ref="E20" ns1:id="rId19"/>
+    <hyperlink ref="E21" ns1:id="rId20"/>
+    <hyperlink ref="E22" ns1:id="rId21"/>
+    <hyperlink ref="E23" ns1:id="rId22"/>
+    <hyperlink ref="E24" ns1:id="rId23"/>
+    <hyperlink ref="E25" ns1:id="rId24"/>
+    <hyperlink ref="E26" ns1:id="rId25"/>
+    <hyperlink ref="E27" ns1:id="rId26"/>
+    <hyperlink ref="E28" ns1:id="rId27"/>
+    <hyperlink ref="E29" ns1:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1453,6 +1473,11 @@
           <t>官网/系列主页链接</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>openalex_source_id</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1467,7 +1492,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>业界顶级(无CCF)</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1507,6 +1532,11 @@
           <t>https://neurips.cc/</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>S4306420609</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -1624,7 +1654,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>ACM SIGSOFT Symposium on Foundations of Software Engineering (FSE)</t>
+          <t>ACM International Conference on the Foundations of Software Engineering</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
@@ -1764,7 +1794,7 @@
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>CCF B</t>
+          <t>CCF C</t>
         </is>
       </c>
       <c r="D13" s="26" t="inlineStr">
@@ -1775,6 +1805,11 @@
       <c r="E13" s="28" t="inlineStr">
         <is>
           <t>https://conf.researchr.org/series/msr</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S4306420528</t>
         </is>
       </c>
     </row>
@@ -1980,7 +2015,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>CCF B</t>
+          <t>CCF C</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -1991,6 +2026,11 @@
       <c r="E21" s="17" t="inlineStr">
         <is>
           <t>https://ifca.ai/fc/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S4306418423</t>
         </is>
       </c>
     </row>
@@ -2020,6 +2060,11 @@
           <t>https://www.podc.org/</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S4306420730</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
@@ -2034,7 +2079,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>高水平专业会</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -2061,7 +2106,7 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>高水平专业会</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
@@ -2115,7 +2160,7 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>业界高认可</t>
+          <t>CCF C</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -2126,6 +2171,11 @@
       <c r="E26" s="23" t="inlineStr">
         <is>
           <t>https://qrs.ieee.org/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S4363608552</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2246,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>业界高认可</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr">
@@ -2223,7 +2273,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>业界高认可</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -2250,7 +2300,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>保底级别</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
@@ -2266,36 +2316,36 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink ref="E2" ns1:id="rId1"/>
+    <hyperlink ref="E3" ns1:id="rId2"/>
+    <hyperlink ref="E4" ns1:id="rId3"/>
+    <hyperlink ref="E5" ns1:id="rId4"/>
+    <hyperlink ref="E6" ns1:id="rId5"/>
+    <hyperlink ref="E7" ns1:id="rId6"/>
+    <hyperlink ref="E8" ns1:id="rId7"/>
+    <hyperlink ref="E9" ns1:id="rId8"/>
+    <hyperlink ref="E10" ns1:id="rId9"/>
+    <hyperlink ref="E11" ns1:id="rId10"/>
+    <hyperlink ref="E12" ns1:id="rId11"/>
+    <hyperlink ref="E13" ns1:id="rId12"/>
+    <hyperlink ref="E14" ns1:id="rId13"/>
+    <hyperlink ref="E15" ns1:id="rId14"/>
+    <hyperlink ref="E16" ns1:id="rId15"/>
+    <hyperlink ref="E17" ns1:id="rId16"/>
+    <hyperlink ref="E18" ns1:id="rId17"/>
+    <hyperlink ref="E19" ns1:id="rId18"/>
+    <hyperlink ref="E20" ns1:id="rId19"/>
+    <hyperlink ref="E21" ns1:id="rId20"/>
+    <hyperlink ref="E22" ns1:id="rId21"/>
+    <hyperlink ref="E23" ns1:id="rId22"/>
+    <hyperlink ref="E24" ns1:id="rId23"/>
+    <hyperlink ref="E25" ns1:id="rId24"/>
+    <hyperlink ref="E26" ns1:id="rId25"/>
+    <hyperlink ref="E27" ns1:id="rId26"/>
+    <hyperlink ref="E28" ns1:id="rId27"/>
+    <hyperlink ref="E29" ns1:id="rId28"/>
+    <hyperlink ref="E30" ns1:id="rId29"/>
+    <hyperlink ref="E31" ns1:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
